--- a/employee_information_forms/020_employee_physical_examination_questionnaire--employee_information_forms.xlsx
+++ b/employee_information_forms/020_employee_physical_examination_questionnaire--employee_information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>employee_physical_examination_questionnaire</t>
+          <t>employee_physical_examination_questionnaire_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Employee Information Forms</t>
+          <t>Medical Status</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_1</t>
+          <t>physical_examination_questionnaire_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Physical Examination</t>
+          <t>Recent Injuries or Illnesses</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_2</t>
+          <t>physical_examination_questionnaire_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Examination Date</t>
+          <t>Height (in cm)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_3</t>
+          <t>physical_examination_questionnaire_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Physical Examination</t>
+          <t>Weight (in kg)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_4</t>
+          <t>physical_examination_questionnaire_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Physical Examination</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_5</t>
+          <t>blood_pressure</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Medical Office</t>
+          <t>Blood Pressure (mmHg)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_6</t>
+          <t>heart_rate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Health Status</t>
+          <t>Heart Rate (bpm)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_7</t>
+          <t>medical_history</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Health Status</t>
+          <t>Medical History</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_8</t>
+          <t>medication_history</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Health Status</t>
+          <t>Medication History</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_9</t>
+          <t>allergy_question</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Health Status</t>
+          <t>Allergies</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_10</t>
+          <t>medical_condition</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Health Status</t>
+          <t>Medical Conditions</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_11</t>
+          <t>chronic_condition</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Health Status</t>
+          <t>Chronic Conditions</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_12</t>
+          <t>smoke_tobacco</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Health Status</t>
+          <t>Smoking or Tobacco Use</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,16 +819,108 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_13</t>
+          <t>medical_device</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Health Status</t>
+          <t>Medical Devices or Equipment</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>implants_prosthetics</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Implants or Prosthetics</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>regular_medication</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Regular Medications</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>medical_procedure</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Medical Procedures or Surgeries</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>medical_insurance</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Medical Insurance</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -873,102 +965,238 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_1_choices</t>
+          <t>allergy_question_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_1_choices</t>
+          <t>allergy_question_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_5_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_5_choices</t>
+          <t>medical_condition_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_6_choices</t>
+          <t>chronic_condition_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>physical_examination_questionnaire_6_choices</t>
+          <t>chronic_condition_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>inactive</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Inactive</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>smoke_tobacco_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>smoke_tobacco_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>regular_medication_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>regular_medication_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>medical_procedure_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>medical_procedure_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>medical_insurance_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>medical_insurance_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
